--- a/docs/update-schedule.xlsx
+++ b/docs/update-schedule.xlsx
@@ -403,16 +403,16 @@
     <t xml:space="preserve">ブログ記事</t>
   </si>
   <si>
-    <t xml:space="preserve">月1本</t>
-  </si>
-  <si>
-    <t xml:space="preserve">月末までに1本</t>
+    <t xml:space="preserve">月2本</t>
+  </si>
+  <si>
+    <t xml:space="preserve">月の前半・後半に1本ずつ</t>
   </si>
   <si>
     <t xml:space="preserve">検索の入り口を増やす。本数より、疑問にきちんと答える質のほうが効く</t>
   </si>
   <si>
-    <t xml:space="preserve">「ブログネタ帳」シート参照。下書きはClaudeに依頼し、内容の確認に集中する</t>
+    <t xml:space="preserve">「ブログネタ帳」シート参照。下書きはClaudeに依頼し、内容の確認に集中する。確認が負担な月は1本に落としてよい</t>
   </si>
   <si>
     <t xml:space="preserve">既存記事の見直し</t>
@@ -1157,7 +1157,7 @@
     <t xml:space="preserve">「今年もありがとうございました」投稿。雪止め・落雪のネタ</t>
   </si>
   <si>
-    <t xml:space="preserve">ブログネタ帳　— 月1本のストック。下書きはClaudeに依頼できます</t>
+    <t xml:space="preserve">ブログネタ帳　— 月2本のペースなら約5か月分。ネタ切れ前にClaudeに追加を頼めます</t>
   </si>
   <si>
     <t xml:space="preserve">ネタ</t>
@@ -2441,11 +2441,11 @@
         <v>90</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G12" s="11" t="n">
         <f aca="false">E12*F12</f>
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="H12" s="6" t="s">
         <v>33</v>
@@ -2666,12 +2666,12 @@
       <c r="F19" s="21"/>
       <c r="G19" s="23" t="n">
         <f aca="false">SUM(G6:G18)</f>
-        <v>484.15</v>
+        <v>574.15</v>
       </c>
       <c r="H19" s="21"/>
       <c r="I19" s="24" t="str">
         <f aca="false">"1か月あたり約 "&amp;ROUND(G19/60,1)&amp;" 時間（1日あたり約 "&amp;ROUND(G19/30,0)&amp;" 分）"</f>
-        <v>1か月あたり約 8.1 時間（1日あたり約 16 分）</v>
+        <v>1か月あたり約 9.6 時間（1日あたり約 19 分）</v>
       </c>
       <c r="J19" s="21"/>
     </row>

--- a/docs/update-schedule.xlsx
+++ b/docs/update-schedule.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="192">
   <si>
     <t xml:space="preserve">辰弥塗装工業　SEO・MEO 更新スケジュール</t>
   </si>
@@ -1157,7 +1157,79 @@
     <t xml:space="preserve">「今年もありがとうございました」投稿。雪止め・落雪のネタ</t>
   </si>
   <si>
-    <t xml:space="preserve">ブログネタ帳　— 月2本のペースなら約5か月分。ネタ切れ前にClaudeに追加を頼めます</t>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="13"/>
+        <color rgb="FF0B4A5F"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">ブログネタ帳　— 優先順位と根拠は </t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="13"/>
+        <color rgb="FF0B4A5F"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">docs/keyword-research-2026-08.xlsx</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="13"/>
+        <color rgb="FF0B4A5F"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">（</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="13"/>
+        <color rgb="FF0B4A5F"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="13"/>
+        <color rgb="FF0B4A5F"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="13"/>
+        <color rgb="FF0B4A5F"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">8</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="13"/>
+        <color rgb="FF0B4A5F"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月のキーワード調査）を参照</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">ネタ</t>
@@ -1421,10 +1493,33 @@
     <t xml:space="preserve">外壁の色選びのコツと失敗例</t>
   </si>
   <si>
-    <t xml:space="preserve">外壁塗装 色 選び方 失敗</t>
-  </si>
-  <si>
-    <t xml:space="preserve">施工事例の写真を使う。カラーシミュレーションの話も</t>
+    <t xml:space="preserve">外壁塗装 色見本(2,400) / 人気色(1,900) / 色選び シュミレーション(1,900)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFE2661F"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">優先度</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFE2661F"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">UP</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">キーワード調査で需要が想定以上と判明（合計1万超/月）。施工事例の写真がそのまま使える。9月前半の本に</t>
   </si>
   <si>
     <t xml:space="preserve">よくあるご質問まとめ</t>
@@ -1464,6 +1559,192 @@
   </si>
   <si>
     <t xml:space="preserve">適用可否は個別判断。「保険で無料」と断定しない書き方が必須（docs/line.md 参照）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">外壁塗装を</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">20</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年していないとどうなる？</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">外壁塗装 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">20</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年してない </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/ 30</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年してない（知恵袋の質問需要</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">位）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">9</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月後半</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">悩み系の頂点。凍害・雪という秋田固有の劣化を絡めれば全国サイトに勝てる。「点検だけでも</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">OK</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">」と相性が良い</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">塗装と張り替え（カバー工法）どっちが安い？</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">外壁塗装 張り替え どっち </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">サイディング 張替え</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Meiryo"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">11</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">検討初期の比較記事。張替えが向くケースも正直に書くと信頼になる</t>
   </si>
   <si>
     <t xml:space="preserve">実績記録　— やったことを1行ずつ足していくだけ</t>
@@ -1522,7 +1803,7 @@
     <numFmt numFmtId="165" formatCode="0.##"/>
     <numFmt numFmtId="166" formatCode="0"/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="29">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1656,6 +1937,21 @@
     </font>
     <font>
       <b val="true"/>
+      <sz val="13"/>
+      <color rgb="FF0B4A5F"/>
+      <name val="WenQuanYi Zen Hei"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="13"/>
+      <color rgb="FF0B4A5F"/>
+      <name val="Meiryo"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
       <sz val="10"/>
       <color rgb="FFE2661F"/>
       <name val="WenQuanYi Zen Hei"/>
@@ -1665,9 +1961,27 @@
     <font>
       <b val="true"/>
       <sz val="10"/>
+      <color rgb="FFE2661F"/>
+      <name val="WenQuanYi Zen Hei"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
       <color rgb="FFB00000"/>
       <name val="WenQuanYi Zen Hei"/>
       <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="WenQuanYi Zen Hei"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Meiryo"/>
+      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
@@ -1781,7 +2095,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="41">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1894,19 +2208,51 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="19" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="24" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="25" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2902,7 +3248,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="38"/>
@@ -2913,7 +3259,7 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="28" t="s">
         <v>132</v>
       </c>
     </row>
@@ -2944,7 +3290,7 @@
       <c r="C4" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="D4" s="28" t="s">
+      <c r="D4" s="29" t="s">
         <v>141</v>
       </c>
       <c r="E4" s="6" t="s">
@@ -3063,19 +3409,19 @@
       <c r="C11" s="15" t="s">
         <v>145</v>
       </c>
-      <c r="D11" s="15" t="s">
-        <v>146</v>
+      <c r="D11" s="30" t="s">
+        <v>166</v>
       </c>
       <c r="E11" s="15" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="8" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C12" s="8" t="s">
         <v>145</v>
@@ -3084,24 +3430,58 @@
         <v>146</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="15" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C13" s="15" t="s">
         <v>145</v>
       </c>
-      <c r="D13" s="29" t="s">
-        <v>172</v>
+      <c r="D13" s="31" t="s">
+        <v>173</v>
       </c>
       <c r="E13" s="15" t="s">
-        <v>173</v>
+        <v>174</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="32" t="s">
+        <v>175</v>
+      </c>
+      <c r="B14" s="32" t="s">
+        <v>176</v>
+      </c>
+      <c r="C14" s="33" t="s">
+        <v>177</v>
+      </c>
+      <c r="D14" s="34" t="s">
+        <v>166</v>
+      </c>
+      <c r="E14" s="32" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="35" t="s">
+        <v>179</v>
+      </c>
+      <c r="B15" s="35" t="s">
+        <v>180</v>
+      </c>
+      <c r="C15" s="36" t="s">
+        <v>181</v>
+      </c>
+      <c r="D15" s="37" t="s">
+        <v>146</v>
+      </c>
+      <c r="E15" s="35" t="s">
+        <v>182</v>
       </c>
     </row>
   </sheetData>
@@ -3131,221 +3511,221 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="25" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>175</v>
+        <v>184</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>3</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>177</v>
+        <v>186</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="30" t="s">
-        <v>179</v>
-      </c>
-      <c r="B5" s="30" t="s">
-        <v>180</v>
-      </c>
-      <c r="C5" s="31" t="s">
-        <v>181</v>
-      </c>
-      <c r="D5" s="31" t="s">
-        <v>182</v>
+      <c r="A5" s="38" t="s">
+        <v>188</v>
+      </c>
+      <c r="B5" s="38" t="s">
+        <v>189</v>
+      </c>
+      <c r="C5" s="39" t="s">
+        <v>190</v>
+      </c>
+      <c r="D5" s="39" t="s">
+        <v>191</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="32"/>
-      <c r="B6" s="32"/>
-      <c r="C6" s="32"/>
-      <c r="D6" s="32"/>
+      <c r="A6" s="40"/>
+      <c r="B6" s="40"/>
+      <c r="C6" s="40"/>
+      <c r="D6" s="40"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="32"/>
-      <c r="B7" s="32"/>
-      <c r="C7" s="32"/>
-      <c r="D7" s="32"/>
+      <c r="A7" s="40"/>
+      <c r="B7" s="40"/>
+      <c r="C7" s="40"/>
+      <c r="D7" s="40"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="32"/>
-      <c r="B8" s="32"/>
-      <c r="C8" s="32"/>
-      <c r="D8" s="32"/>
+      <c r="A8" s="40"/>
+      <c r="B8" s="40"/>
+      <c r="C8" s="40"/>
+      <c r="D8" s="40"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="32"/>
-      <c r="B9" s="32"/>
-      <c r="C9" s="32"/>
-      <c r="D9" s="32"/>
+      <c r="A9" s="40"/>
+      <c r="B9" s="40"/>
+      <c r="C9" s="40"/>
+      <c r="D9" s="40"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="32"/>
-      <c r="B10" s="32"/>
-      <c r="C10" s="32"/>
-      <c r="D10" s="32"/>
+      <c r="A10" s="40"/>
+      <c r="B10" s="40"/>
+      <c r="C10" s="40"/>
+      <c r="D10" s="40"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="32"/>
-      <c r="B11" s="32"/>
-      <c r="C11" s="32"/>
-      <c r="D11" s="32"/>
+      <c r="A11" s="40"/>
+      <c r="B11" s="40"/>
+      <c r="C11" s="40"/>
+      <c r="D11" s="40"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="32"/>
-      <c r="B12" s="32"/>
-      <c r="C12" s="32"/>
-      <c r="D12" s="32"/>
+      <c r="A12" s="40"/>
+      <c r="B12" s="40"/>
+      <c r="C12" s="40"/>
+      <c r="D12" s="40"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="32"/>
-      <c r="B13" s="32"/>
-      <c r="C13" s="32"/>
-      <c r="D13" s="32"/>
+      <c r="A13" s="40"/>
+      <c r="B13" s="40"/>
+      <c r="C13" s="40"/>
+      <c r="D13" s="40"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="32"/>
-      <c r="B14" s="32"/>
-      <c r="C14" s="32"/>
-      <c r="D14" s="32"/>
+      <c r="A14" s="40"/>
+      <c r="B14" s="40"/>
+      <c r="C14" s="40"/>
+      <c r="D14" s="40"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="32"/>
-      <c r="B15" s="32"/>
-      <c r="C15" s="32"/>
-      <c r="D15" s="32"/>
+      <c r="A15" s="40"/>
+      <c r="B15" s="40"/>
+      <c r="C15" s="40"/>
+      <c r="D15" s="40"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="32"/>
-      <c r="B16" s="32"/>
-      <c r="C16" s="32"/>
-      <c r="D16" s="32"/>
+      <c r="A16" s="40"/>
+      <c r="B16" s="40"/>
+      <c r="C16" s="40"/>
+      <c r="D16" s="40"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="32"/>
-      <c r="B17" s="32"/>
-      <c r="C17" s="32"/>
-      <c r="D17" s="32"/>
+      <c r="A17" s="40"/>
+      <c r="B17" s="40"/>
+      <c r="C17" s="40"/>
+      <c r="D17" s="40"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="32"/>
-      <c r="B18" s="32"/>
-      <c r="C18" s="32"/>
-      <c r="D18" s="32"/>
+      <c r="A18" s="40"/>
+      <c r="B18" s="40"/>
+      <c r="C18" s="40"/>
+      <c r="D18" s="40"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="32"/>
-      <c r="B19" s="32"/>
-      <c r="C19" s="32"/>
-      <c r="D19" s="32"/>
+      <c r="A19" s="40"/>
+      <c r="B19" s="40"/>
+      <c r="C19" s="40"/>
+      <c r="D19" s="40"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="32"/>
-      <c r="B20" s="32"/>
-      <c r="C20" s="32"/>
-      <c r="D20" s="32"/>
+      <c r="A20" s="40"/>
+      <c r="B20" s="40"/>
+      <c r="C20" s="40"/>
+      <c r="D20" s="40"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="32"/>
-      <c r="B21" s="32"/>
-      <c r="C21" s="32"/>
-      <c r="D21" s="32"/>
+      <c r="A21" s="40"/>
+      <c r="B21" s="40"/>
+      <c r="C21" s="40"/>
+      <c r="D21" s="40"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="32"/>
-      <c r="B22" s="32"/>
-      <c r="C22" s="32"/>
-      <c r="D22" s="32"/>
+      <c r="A22" s="40"/>
+      <c r="B22" s="40"/>
+      <c r="C22" s="40"/>
+      <c r="D22" s="40"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="32"/>
-      <c r="B23" s="32"/>
-      <c r="C23" s="32"/>
-      <c r="D23" s="32"/>
+      <c r="A23" s="40"/>
+      <c r="B23" s="40"/>
+      <c r="C23" s="40"/>
+      <c r="D23" s="40"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="32"/>
-      <c r="B24" s="32"/>
-      <c r="C24" s="32"/>
-      <c r="D24" s="32"/>
+      <c r="A24" s="40"/>
+      <c r="B24" s="40"/>
+      <c r="C24" s="40"/>
+      <c r="D24" s="40"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="32"/>
-      <c r="B25" s="32"/>
-      <c r="C25" s="32"/>
-      <c r="D25" s="32"/>
+      <c r="A25" s="40"/>
+      <c r="B25" s="40"/>
+      <c r="C25" s="40"/>
+      <c r="D25" s="40"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="32"/>
-      <c r="B26" s="32"/>
-      <c r="C26" s="32"/>
-      <c r="D26" s="32"/>
+      <c r="A26" s="40"/>
+      <c r="B26" s="40"/>
+      <c r="C26" s="40"/>
+      <c r="D26" s="40"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="32"/>
-      <c r="B27" s="32"/>
-      <c r="C27" s="32"/>
-      <c r="D27" s="32"/>
+      <c r="A27" s="40"/>
+      <c r="B27" s="40"/>
+      <c r="C27" s="40"/>
+      <c r="D27" s="40"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="32"/>
-      <c r="B28" s="32"/>
-      <c r="C28" s="32"/>
-      <c r="D28" s="32"/>
+      <c r="A28" s="40"/>
+      <c r="B28" s="40"/>
+      <c r="C28" s="40"/>
+      <c r="D28" s="40"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="32"/>
-      <c r="B29" s="32"/>
-      <c r="C29" s="32"/>
-      <c r="D29" s="32"/>
+      <c r="A29" s="40"/>
+      <c r="B29" s="40"/>
+      <c r="C29" s="40"/>
+      <c r="D29" s="40"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="32"/>
-      <c r="B30" s="32"/>
-      <c r="C30" s="32"/>
-      <c r="D30" s="32"/>
+      <c r="A30" s="40"/>
+      <c r="B30" s="40"/>
+      <c r="C30" s="40"/>
+      <c r="D30" s="40"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="32"/>
-      <c r="B31" s="32"/>
-      <c r="C31" s="32"/>
-      <c r="D31" s="32"/>
+      <c r="A31" s="40"/>
+      <c r="B31" s="40"/>
+      <c r="C31" s="40"/>
+      <c r="D31" s="40"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="32"/>
-      <c r="B32" s="32"/>
-      <c r="C32" s="32"/>
-      <c r="D32" s="32"/>
+      <c r="A32" s="40"/>
+      <c r="B32" s="40"/>
+      <c r="C32" s="40"/>
+      <c r="D32" s="40"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="32"/>
-      <c r="B33" s="32"/>
-      <c r="C33" s="32"/>
-      <c r="D33" s="32"/>
+      <c r="A33" s="40"/>
+      <c r="B33" s="40"/>
+      <c r="C33" s="40"/>
+      <c r="D33" s="40"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="32"/>
-      <c r="B34" s="32"/>
-      <c r="C34" s="32"/>
-      <c r="D34" s="32"/>
+      <c r="A34" s="40"/>
+      <c r="B34" s="40"/>
+      <c r="C34" s="40"/>
+      <c r="D34" s="40"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="32"/>
-      <c r="B35" s="32"/>
-      <c r="C35" s="32"/>
-      <c r="D35" s="32"/>
+      <c r="A35" s="40"/>
+      <c r="B35" s="40"/>
+      <c r="C35" s="40"/>
+      <c r="D35" s="40"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/docs/update-schedule.xlsx
+++ b/docs/update-schedule.xlsx
@@ -1157,505 +1157,350 @@
     <t xml:space="preserve">「今年もありがとうございました」投稿。雪止め・落雪のネタ</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="13"/>
-        <color rgb="FF0B4A5F"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">ブログネタ帳　— 優先順位と根拠は </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="13"/>
-        <color rgb="FF0B4A5F"/>
+    <t xml:space="preserve">ブログネタ帳　— 優先順位と根拠は docs/keyword-research-2026-08.xlsx（2026年8月のキーワード調査）を参照</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ネタ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">狙う検索の言葉</t>
+  </si>
+  <si>
+    <t xml:space="preserve">おすすめの時期</t>
+  </si>
+  <si>
+    <t xml:space="preserve">状態</t>
+  </si>
+  <si>
+    <t xml:space="preserve">メモ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">秋田市の外壁塗装に使える補助金・助成金</t>
+  </si>
+  <si>
+    <t xml:space="preserve">秋田市 外壁塗装 補助金</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月（毎年更新）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">公開済み</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026-08-26 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">公開（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/blog/2026-08-akita-gaiheki-hojokin/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">）。毎年</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月に新年度の数値へ更新する</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">塗料の種類と耐用年数の選び方</t>
+  </si>
+  <si>
+    <t xml:space="preserve">外壁塗装 塗料 種類 / シリコン フッ素 違い</t>
+  </si>
+  <si>
+    <t xml:space="preserve">いつでも</t>
+  </si>
+  <si>
+    <t xml:space="preserve">未着手</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">services.toml </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">の料金・保証年数と食い違わないように</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">外壁塗装の見積書の見方・比べ方</t>
+  </si>
+  <si>
+    <t xml:space="preserve">外壁塗装 見積り 見方</t>
+  </si>
+  <si>
+    <t xml:space="preserve">「一式」表記への注意など。相見積り歓迎の姿勢が信頼になる</t>
+  </si>
+  <si>
+    <t xml:space="preserve">訪問販売で「今すぐ塗らないと危ない」と言われたら</t>
+  </si>
+  <si>
+    <t xml:space="preserve">外壁塗装 訪問販売 しつこい</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">docs/line.md </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">でも受注につながりやすいと分析済みのテーマ</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">外壁塗装の工事の流れ（足場から完工まで）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">外壁塗装 工事 流れ 日数</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">LINE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">の工期応答の内容を膨らませる。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">日前後の工程表</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">コーキング（目地）の役割と劣化のサイン</t>
+  </si>
+  <si>
+    <t xml:space="preserve">コーキング 劣化 ひび割れ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">施工写真 shokunin-coking.jpg が使える</t>
+  </si>
+  <si>
+    <t xml:space="preserve">雪止め・屋根の雪対策と塗装</t>
+  </si>
+  <si>
+    <t xml:space="preserve">秋田 屋根 雪止め 落雪</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">〜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">12</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">月</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">市の補助金でも雪止め設置は対象工事。冬前に出すと効く</t>
+  </si>
+  <si>
+    <t xml:space="preserve">外壁の色選びのコツと失敗例</t>
+  </si>
+  <si>
+    <t xml:space="preserve">外壁塗装 色見本(2,400) / 人気色(1,900) / 色選び シュミレーション(1,900)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">優先度UP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">キーワード調査で需要が想定以上と判明（合計1万超/月）。施工事例の写真がそのまま使える。9月前半の本に</t>
+  </si>
+  <si>
+    <t xml:space="preserve">よくあるご質問まとめ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">外壁塗装 よくある質問</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">LINE</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">の応答メッセージ（無料・工期・保証・エリア）を記事に再構成</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">火災保険と外壁・屋根の修理の考え方</t>
+  </si>
+  <si>
+    <t xml:space="preserve">屋根 修理 火災保険</t>
+  </si>
+  <si>
+    <t xml:space="preserve">要注意</t>
+  </si>
+  <si>
+    <t xml:space="preserve">適用可否は個別判断。「保険で無料」と断定しない書き方が必須（docs/line.md 参照）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">外壁塗装を20年していないとどうなる？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">外壁塗装 20年してない / 30年してない（知恵袋の質問需要1位）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
         <rFont val="Meiryo"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">docs/keyword-research-2026-08.xlsx</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="13"/>
-        <color rgb="FF0B4A5F"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">（</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="13"/>
-        <color rgb="FF0B4A5F"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2026</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="13"/>
-        <color rgb="FF0B4A5F"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">年</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="13"/>
-        <color rgb="FF0B4A5F"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">8</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="13"/>
-        <color rgb="FF0B4A5F"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">月のキーワード調査）を参照</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">ネタ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">狙う検索の言葉</t>
-  </si>
-  <si>
-    <t xml:space="preserve">おすすめの時期</t>
-  </si>
-  <si>
-    <t xml:space="preserve">状態</t>
-  </si>
-  <si>
-    <t xml:space="preserve">メモ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">秋田市の外壁塗装に使える補助金・助成金</t>
-  </si>
-  <si>
-    <t xml:space="preserve">秋田市 外壁塗装 補助金</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">4</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">月（毎年更新）</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">下書き済み・確認待ち</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">drafts/ </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">に下書きあり。毎年</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">4</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">月に新年度の数値へ更新する</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">塗料の種類と耐用年数の選び方</t>
-  </si>
-  <si>
-    <t xml:space="preserve">外壁塗装 塗料 種類 / シリコン フッ素 違い</t>
-  </si>
-  <si>
-    <t xml:space="preserve">いつでも</t>
-  </si>
-  <si>
-    <t xml:space="preserve">未着手</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">services.toml </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">の料金・保証年数と食い違わないように</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">外壁塗装の見積書の見方・比べ方</t>
-  </si>
-  <si>
-    <t xml:space="preserve">外壁塗装 見積り 見方</t>
-  </si>
-  <si>
-    <t xml:space="preserve">「一式」表記への注意など。相見積り歓迎の姿勢が信頼になる</t>
-  </si>
-  <si>
-    <t xml:space="preserve">訪問販売で「今すぐ塗らないと危ない」と言われたら</t>
-  </si>
-  <si>
-    <t xml:space="preserve">外壁塗装 訪問販売 しつこい</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">docs/line.md </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">でも受注につながりやすいと分析済みのテーマ</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">外壁塗装の工事の流れ（足場から完工まで）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">外壁塗装 工事 流れ 日数</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">LINE</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">の工期応答の内容を膨らませる。</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">10</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">日前後の工程表</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">コーキング（目地）の役割と劣化のサイン</t>
-  </si>
-  <si>
-    <t xml:space="preserve">コーキング 劣化 ひび割れ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">施工写真 shokunin-coking.jpg が使える</t>
-  </si>
-  <si>
-    <t xml:space="preserve">雪止め・屋根の雪対策と塗装</t>
-  </si>
-  <si>
-    <t xml:space="preserve">秋田 屋根 雪止め 落雪</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">10</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">〜</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">12</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">月</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">市の補助金でも雪止め設置は対象工事。冬前に出すと効く</t>
-  </si>
-  <si>
-    <t xml:space="preserve">外壁の色選びのコツと失敗例</t>
-  </si>
-  <si>
-    <t xml:space="preserve">外壁塗装 色見本(2,400) / 人気色(1,900) / 色選び シュミレーション(1,900)</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FFE2661F"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">優先度</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FFE2661F"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">UP</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">キーワード調査で需要が想定以上と判明（合計1万超/月）。施工事例の写真がそのまま使える。9月前半の本に</t>
-  </si>
-  <si>
-    <t xml:space="preserve">よくあるご質問まとめ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">外壁塗装 よくある質問</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">LINE</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">の応答メッセージ（無料・工期・保証・エリア）を記事に再構成</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">火災保険と外壁・屋根の修理の考え方</t>
-  </si>
-  <si>
-    <t xml:space="preserve">屋根 修理 火災保険</t>
-  </si>
-  <si>
-    <t xml:space="preserve">要注意</t>
-  </si>
-  <si>
-    <t xml:space="preserve">適用可否は個別判断。「保険で無料」と断定しない書き方が必須（docs/line.md 参照）</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">外壁塗装を</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">20</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">年していないとどうなる？</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">外壁塗装 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">20</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">年してない </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/ 30</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">年してない（知恵袋の質問需要</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">位）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
       <t xml:space="preserve">9</t>
     </r>
     <r>
@@ -1668,61 +1513,13 @@
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">悩み系の頂点。凍害・雪という秋田固有の劣化を絡めれば全国サイトに勝てる。「点検だけでも</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">OK</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">」と相性が良い</t>
-    </r>
+    <t xml:space="preserve">悩み系の頂点。凍害・雪という秋田固有の劣化を絡めれば全国サイトに勝てる。「点検だけでもOK」と相性が良い</t>
   </si>
   <si>
     <t xml:space="preserve">塗装と張り替え（カバー工法）どっちが安い？</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">外壁塗装 張り替え どっち </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Meiryo"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/ </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="WenQuanYi Zen Hei"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">サイディング 張替え</t>
-    </r>
+    <t xml:space="preserve">外壁塗装 張り替え どっち / サイディング 張替え</t>
   </si>
   <si>
     <r>
@@ -1803,7 +1600,7 @@
     <numFmt numFmtId="165" formatCode="0.##"/>
     <numFmt numFmtId="166" formatCode="0"/>
   </numFmts>
-  <fonts count="29">
+  <fonts count="28">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1937,18 +1734,10 @@
     </font>
     <font>
       <b val="true"/>
-      <sz val="13"/>
-      <color rgb="FF0B4A5F"/>
+      <sz val="10"/>
+      <color rgb="FF00758F"/>
       <name val="WenQuanYi Zen Hei"/>
       <family val="2"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="13"/>
-      <color rgb="FF0B4A5F"/>
-      <name val="Meiryo"/>
-      <family val="0"/>
-      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
@@ -1957,13 +1746,6 @@
       <name val="WenQuanYi Zen Hei"/>
       <family val="2"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="10"/>
-      <color rgb="FFE2661F"/>
-      <name val="WenQuanYi Zen Hei"/>
-      <family val="2"/>
     </font>
     <font>
       <b val="true"/>
@@ -1977,12 +1759,18 @@
       <sz val="10"/>
       <name val="WenQuanYi Zen Hei"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Meiryo"/>
       <family val="0"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="WenQuanYi Zen Hei"/>
+      <family val="2"/>
     </font>
     <font>
       <i val="true"/>
@@ -2095,7 +1883,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="40">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2208,12 +1996,28 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="21" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="19" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
@@ -2224,35 +2028,15 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="24" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="25" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2284,7 +2068,7 @@
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FF808000"/>
       <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FF00758F"/>
       <rgbColor rgb="FFBBCDD4"/>
       <rgbColor rgb="FF888888"/>
       <rgbColor rgb="FF9999FF"/>
@@ -3259,7 +3043,7 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="25" t="s">
         <v>132</v>
       </c>
     </row>
@@ -3290,7 +3074,7 @@
       <c r="C4" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="D4" s="29" t="s">
+      <c r="D4" s="28" t="s">
         <v>141</v>
       </c>
       <c r="E4" s="6" t="s">
@@ -3409,7 +3193,7 @@
       <c r="C11" s="15" t="s">
         <v>145</v>
       </c>
-      <c r="D11" s="30" t="s">
+      <c r="D11" s="29" t="s">
         <v>166</v>
       </c>
       <c r="E11" s="15" t="s">
@@ -3443,44 +3227,44 @@
       <c r="C13" s="15" t="s">
         <v>145</v>
       </c>
-      <c r="D13" s="31" t="s">
+      <c r="D13" s="30" t="s">
         <v>173</v>
       </c>
       <c r="E13" s="15" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="32" t="s">
+    <row r="14" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="31" t="s">
         <v>175</v>
       </c>
-      <c r="B14" s="32" t="s">
+      <c r="B14" s="31" t="s">
         <v>176</v>
       </c>
-      <c r="C14" s="33" t="s">
+      <c r="C14" s="32" t="s">
         <v>177</v>
       </c>
-      <c r="D14" s="34" t="s">
+      <c r="D14" s="33" t="s">
         <v>166</v>
       </c>
-      <c r="E14" s="32" t="s">
+      <c r="E14" s="31" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="35" t="s">
+    <row r="15" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="34" t="s">
         <v>179</v>
       </c>
-      <c r="B15" s="35" t="s">
+      <c r="B15" s="34" t="s">
         <v>180</v>
       </c>
-      <c r="C15" s="36" t="s">
+      <c r="C15" s="35" t="s">
         <v>181</v>
       </c>
-      <c r="D15" s="37" t="s">
+      <c r="D15" s="36" t="s">
         <v>146</v>
       </c>
-      <c r="E15" s="35" t="s">
+      <c r="E15" s="34" t="s">
         <v>182</v>
       </c>
     </row>
@@ -3534,198 +3318,198 @@
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="38" t="s">
+      <c r="A5" s="37" t="s">
         <v>188</v>
       </c>
-      <c r="B5" s="38" t="s">
+      <c r="B5" s="37" t="s">
         <v>189</v>
       </c>
-      <c r="C5" s="39" t="s">
+      <c r="C5" s="38" t="s">
         <v>190</v>
       </c>
-      <c r="D5" s="39" t="s">
+      <c r="D5" s="38" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="40"/>
-      <c r="B6" s="40"/>
-      <c r="C6" s="40"/>
-      <c r="D6" s="40"/>
+      <c r="A6" s="39"/>
+      <c r="B6" s="39"/>
+      <c r="C6" s="39"/>
+      <c r="D6" s="39"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="40"/>
-      <c r="B7" s="40"/>
-      <c r="C7" s="40"/>
-      <c r="D7" s="40"/>
+      <c r="A7" s="39"/>
+      <c r="B7" s="39"/>
+      <c r="C7" s="39"/>
+      <c r="D7" s="39"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="40"/>
-      <c r="B8" s="40"/>
-      <c r="C8" s="40"/>
-      <c r="D8" s="40"/>
+      <c r="A8" s="39"/>
+      <c r="B8" s="39"/>
+      <c r="C8" s="39"/>
+      <c r="D8" s="39"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="40"/>
-      <c r="B9" s="40"/>
-      <c r="C9" s="40"/>
-      <c r="D9" s="40"/>
+      <c r="A9" s="39"/>
+      <c r="B9" s="39"/>
+      <c r="C9" s="39"/>
+      <c r="D9" s="39"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="40"/>
-      <c r="B10" s="40"/>
-      <c r="C10" s="40"/>
-      <c r="D10" s="40"/>
+      <c r="A10" s="39"/>
+      <c r="B10" s="39"/>
+      <c r="C10" s="39"/>
+      <c r="D10" s="39"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="40"/>
-      <c r="B11" s="40"/>
-      <c r="C11" s="40"/>
-      <c r="D11" s="40"/>
+      <c r="A11" s="39"/>
+      <c r="B11" s="39"/>
+      <c r="C11" s="39"/>
+      <c r="D11" s="39"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="40"/>
-      <c r="B12" s="40"/>
-      <c r="C12" s="40"/>
-      <c r="D12" s="40"/>
+      <c r="A12" s="39"/>
+      <c r="B12" s="39"/>
+      <c r="C12" s="39"/>
+      <c r="D12" s="39"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="40"/>
-      <c r="B13" s="40"/>
-      <c r="C13" s="40"/>
-      <c r="D13" s="40"/>
+      <c r="A13" s="39"/>
+      <c r="B13" s="39"/>
+      <c r="C13" s="39"/>
+      <c r="D13" s="39"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="40"/>
-      <c r="B14" s="40"/>
-      <c r="C14" s="40"/>
-      <c r="D14" s="40"/>
+      <c r="A14" s="39"/>
+      <c r="B14" s="39"/>
+      <c r="C14" s="39"/>
+      <c r="D14" s="39"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="40"/>
-      <c r="B15" s="40"/>
-      <c r="C15" s="40"/>
-      <c r="D15" s="40"/>
+      <c r="A15" s="39"/>
+      <c r="B15" s="39"/>
+      <c r="C15" s="39"/>
+      <c r="D15" s="39"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="40"/>
-      <c r="B16" s="40"/>
-      <c r="C16" s="40"/>
-      <c r="D16" s="40"/>
+      <c r="A16" s="39"/>
+      <c r="B16" s="39"/>
+      <c r="C16" s="39"/>
+      <c r="D16" s="39"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="40"/>
-      <c r="B17" s="40"/>
-      <c r="C17" s="40"/>
-      <c r="D17" s="40"/>
+      <c r="A17" s="39"/>
+      <c r="B17" s="39"/>
+      <c r="C17" s="39"/>
+      <c r="D17" s="39"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="40"/>
-      <c r="B18" s="40"/>
-      <c r="C18" s="40"/>
-      <c r="D18" s="40"/>
+      <c r="A18" s="39"/>
+      <c r="B18" s="39"/>
+      <c r="C18" s="39"/>
+      <c r="D18" s="39"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="40"/>
-      <c r="B19" s="40"/>
-      <c r="C19" s="40"/>
-      <c r="D19" s="40"/>
+      <c r="A19" s="39"/>
+      <c r="B19" s="39"/>
+      <c r="C19" s="39"/>
+      <c r="D19" s="39"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="40"/>
-      <c r="B20" s="40"/>
-      <c r="C20" s="40"/>
-      <c r="D20" s="40"/>
+      <c r="A20" s="39"/>
+      <c r="B20" s="39"/>
+      <c r="C20" s="39"/>
+      <c r="D20" s="39"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="40"/>
-      <c r="B21" s="40"/>
-      <c r="C21" s="40"/>
-      <c r="D21" s="40"/>
+      <c r="A21" s="39"/>
+      <c r="B21" s="39"/>
+      <c r="C21" s="39"/>
+      <c r="D21" s="39"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="40"/>
-      <c r="B22" s="40"/>
-      <c r="C22" s="40"/>
-      <c r="D22" s="40"/>
+      <c r="A22" s="39"/>
+      <c r="B22" s="39"/>
+      <c r="C22" s="39"/>
+      <c r="D22" s="39"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="40"/>
-      <c r="B23" s="40"/>
-      <c r="C23" s="40"/>
-      <c r="D23" s="40"/>
+      <c r="A23" s="39"/>
+      <c r="B23" s="39"/>
+      <c r="C23" s="39"/>
+      <c r="D23" s="39"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="40"/>
-      <c r="B24" s="40"/>
-      <c r="C24" s="40"/>
-      <c r="D24" s="40"/>
+      <c r="A24" s="39"/>
+      <c r="B24" s="39"/>
+      <c r="C24" s="39"/>
+      <c r="D24" s="39"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="40"/>
-      <c r="B25" s="40"/>
-      <c r="C25" s="40"/>
-      <c r="D25" s="40"/>
+      <c r="A25" s="39"/>
+      <c r="B25" s="39"/>
+      <c r="C25" s="39"/>
+      <c r="D25" s="39"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="40"/>
-      <c r="B26" s="40"/>
-      <c r="C26" s="40"/>
-      <c r="D26" s="40"/>
+      <c r="A26" s="39"/>
+      <c r="B26" s="39"/>
+      <c r="C26" s="39"/>
+      <c r="D26" s="39"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="40"/>
-      <c r="B27" s="40"/>
-      <c r="C27" s="40"/>
-      <c r="D27" s="40"/>
+      <c r="A27" s="39"/>
+      <c r="B27" s="39"/>
+      <c r="C27" s="39"/>
+      <c r="D27" s="39"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="40"/>
-      <c r="B28" s="40"/>
-      <c r="C28" s="40"/>
-      <c r="D28" s="40"/>
+      <c r="A28" s="39"/>
+      <c r="B28" s="39"/>
+      <c r="C28" s="39"/>
+      <c r="D28" s="39"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="40"/>
-      <c r="B29" s="40"/>
-      <c r="C29" s="40"/>
-      <c r="D29" s="40"/>
+      <c r="A29" s="39"/>
+      <c r="B29" s="39"/>
+      <c r="C29" s="39"/>
+      <c r="D29" s="39"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="40"/>
-      <c r="B30" s="40"/>
-      <c r="C30" s="40"/>
-      <c r="D30" s="40"/>
+      <c r="A30" s="39"/>
+      <c r="B30" s="39"/>
+      <c r="C30" s="39"/>
+      <c r="D30" s="39"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="40"/>
-      <c r="B31" s="40"/>
-      <c r="C31" s="40"/>
-      <c r="D31" s="40"/>
+      <c r="A31" s="39"/>
+      <c r="B31" s="39"/>
+      <c r="C31" s="39"/>
+      <c r="D31" s="39"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="40"/>
-      <c r="B32" s="40"/>
-      <c r="C32" s="40"/>
-      <c r="D32" s="40"/>
+      <c r="A32" s="39"/>
+      <c r="B32" s="39"/>
+      <c r="C32" s="39"/>
+      <c r="D32" s="39"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="40"/>
-      <c r="B33" s="40"/>
-      <c r="C33" s="40"/>
-      <c r="D33" s="40"/>
+      <c r="A33" s="39"/>
+      <c r="B33" s="39"/>
+      <c r="C33" s="39"/>
+      <c r="D33" s="39"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="40"/>
-      <c r="B34" s="40"/>
-      <c r="C34" s="40"/>
-      <c r="D34" s="40"/>
+      <c r="A34" s="39"/>
+      <c r="B34" s="39"/>
+      <c r="C34" s="39"/>
+      <c r="D34" s="39"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="40"/>
-      <c r="B35" s="40"/>
-      <c r="C35" s="40"/>
-      <c r="D35" s="40"/>
+      <c r="A35" s="39"/>
+      <c r="B35" s="39"/>
+      <c r="C35" s="39"/>
+      <c r="D35" s="39"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/docs/update-schedule.xlsx
+++ b/docs/update-schedule.xlsx
@@ -1957,7 +1957,7 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>drafts/2026-09-gaiheki-20nen.md（2026-09-06 下書き）。本人確認のうえ9月後半に公開</t>
+          <t>drafts/2026-09-gaiheki-20nen.md（2026-09-06 下書き・本人確認済み）。2026-09-15 公開予約済み</t>
         </is>
       </c>
     </row>

--- a/docs/update-schedule.xlsx
+++ b/docs/update-schedule.xlsx
@@ -1869,14 +1869,14 @@
           <t>いつでも</t>
         </is>
       </c>
-      <c r="D11" s="15" t="inlineStr">
-        <is>
-          <t>優先度UP</t>
+      <c r="D11" s="10" t="inlineStr">
+        <is>
+          <t>公開済み</t>
         </is>
       </c>
       <c r="E11" s="10" t="inlineStr">
         <is>
-          <t>キーワード調査で需要が想定以上と判明（合計1万超/月）。施工事例の写真がそのまま使える。9月前半の本に</t>
+          <t>2026-09-07 公開（/blog/2026-09-gaiheki-iro-erabi/）。カラーシミュレーション需要の受け皿</t>
         </is>
       </c>
     </row>
